--- a/static/standards-correlations/New_Jersey_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/New_Jersey_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$30</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | 2020 NJSLS-CSDT, adopted June 2020 | 8.2 Design Thinking NOT included</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | 2020 NJSLS-CSDT, adopted June 2020 | 8.2 Design Thinking NOT included</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1109,7 +1110,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Ext 3.1F (Compiled, Typed, and Running on Something) contrasts compiled and interpreted execution and what runs the result, and Discovery Systems 8 separates hardware from software as distinct functions.</t>
+          <t>Ext 3.1F (Compiled, Typed, and Running on Something) contrasts compiled and interpreted execution and what runs the result, and Introductory Systems 8 separates hardware from software as distinct functions.</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1606,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>Ext 1.1F (Why a PIN?) evaluates credential strength and Ext 5.3G (Secret Messages / HTTPS) evaluates protected transport. Discovery Systems 10 covers phishing. Extension-only.</t>
+          <t>Ext 1.1F (Why a PIN?) evaluates credential strength and Ext 5.3G (Secret Messages / HTTPS) evaluates protected transport. Introductory Systems 10 covers phishing. Extension-only.</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1767,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1779,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1912,7 @@
 SOURCE NOTE: Codes and statements transcribed from the CodeHS published New Jersey 9-12 Computer Science framework. Adoption and structure verified against nj.gov/education/standards/compsci. Verify wording against the official NJSLS-CSDT document before any formal submission.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.</t>
         </is>
       </c>
